--- a/lms_team_odds1.xlsx
+++ b/lms_team_odds1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paul_\Dropbox\Docs\lms2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05BD869F-7625-49AC-AE50-4F80CD9016D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79550906-258B-4F45-83A8-5C4E31F281A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Odds" sheetId="1" r:id="rId1"/>
@@ -1981,9 +1981,11 @@
       <c r="I35" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J35" s="9"/>
+      <c r="J35" s="9">
+        <v>1.85</v>
+      </c>
       <c r="K35" s="14">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">

--- a/lms_team_odds1.xlsx
+++ b/lms_team_odds1.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paul_\Dropbox\Docs\lms2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79550906-258B-4F45-83A8-5C4E31F281A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB85ECC-BE0C-4484-9A35-DC75F23C307C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Odds" sheetId="1" r:id="rId1"/>
     <sheet name="Team Odds (2)" sheetId="2" r:id="rId2"/>
     <sheet name="Team Odds (3)" sheetId="3" r:id="rId3"/>
+    <sheet name="picks" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">picks!$A$1:$M$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Team Odds'!$A$1:$K$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Team Odds (2)'!$A$1:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Team Odds (3)'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="69">
   <si>
     <t>Team</t>
   </si>
@@ -241,6 +244,12 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>incl</t>
+  </si>
+  <si>
+    <t>KO keep</t>
   </si>
 </sst>
 </file>
@@ -306,7 +315,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,8 +365,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFF1B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -380,11 +419,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -456,6 +610,192 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,6 +804,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFAFF1B1"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2590,7 +2935,7 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="19">
-        <f>COUNTA(L2:N2)</f>
+        <f t="shared" ref="O2:O30" si="0">COUNTA(L2:N2)</f>
         <v>1</v>
       </c>
     </row>
@@ -2634,7 +2979,7 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="19">
-        <f>COUNTA(L3:N3)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2678,7 +3023,7 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="19">
-        <f>COUNTA(L4:N4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2722,7 +3067,7 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="O5" s="19">
-        <f>COUNTA(L5:N5)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2766,7 +3111,7 @@
         <v>65</v>
       </c>
       <c r="O6" s="19">
-        <f>COUNTA(L6:N6)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2812,7 +3157,7 @@
       </c>
       <c r="N7" s="10"/>
       <c r="O7" s="19">
-        <f>COUNTA(L7:N7)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2858,7 +3203,7 @@
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="19">
-        <f>COUNTA(L8:N8)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2904,7 +3249,7 @@
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="19">
-        <f>COUNTA(L9:N9)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2950,7 +3295,7 @@
         <v>65</v>
       </c>
       <c r="O10" s="19">
-        <f>COUNTA(L10:N10)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2994,7 +3339,7 @@
         <v>65</v>
       </c>
       <c r="O11" s="19">
-        <f>COUNTA(L11:N11)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -3038,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="O12" s="19">
-        <f>COUNTA(L12:N12)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -3086,7 +3431,7 @@
         <v>65</v>
       </c>
       <c r="O13" s="20">
-        <f>COUNTA(L13:N13)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3134,7 +3479,7 @@
         <v>65</v>
       </c>
       <c r="O14" s="20">
-        <f>COUNTA(L14:N14)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3182,7 +3527,7 @@
         <v>65</v>
       </c>
       <c r="O15" s="20">
-        <f>COUNTA(L15:N15)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3230,7 +3575,7 @@
         <v>65</v>
       </c>
       <c r="O16" s="20">
-        <f>COUNTA(L16:N16)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3274,7 +3619,7 @@
         <v>65</v>
       </c>
       <c r="O17" s="20">
-        <f>COUNTA(L17:N17)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3320,7 +3665,7 @@
         <v>65</v>
       </c>
       <c r="O18" s="20">
-        <f>COUNTA(L18:N18)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3366,7 +3711,7 @@
         <v>65</v>
       </c>
       <c r="O19" s="20">
-        <f>COUNTA(L19:N19)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3414,7 +3759,7 @@
         <v>65</v>
       </c>
       <c r="O20" s="20">
-        <f>COUNTA(L20:N20)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3462,7 +3807,7 @@
         <v>65</v>
       </c>
       <c r="O21" s="20">
-        <f>COUNTA(L21:N21)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3510,7 +3855,7 @@
         <v>65</v>
       </c>
       <c r="O22" s="20">
-        <f>COUNTA(L22:N22)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3558,7 +3903,7 @@
         <v>65</v>
       </c>
       <c r="O23" s="20">
-        <f>COUNTA(L23:N23)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3606,7 +3951,7 @@
         <v>65</v>
       </c>
       <c r="O24" s="20">
-        <f>COUNTA(L24:N24)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3654,7 +3999,7 @@
         <v>65</v>
       </c>
       <c r="O25" s="20">
-        <f>COUNTA(L25:N25)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3702,7 +4047,7 @@
         <v>65</v>
       </c>
       <c r="O26" s="20">
-        <f>COUNTA(L26:N26)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3750,7 +4095,7 @@
         <v>65</v>
       </c>
       <c r="O27" s="20">
-        <f>COUNTA(L27:N27)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3796,7 +4141,7 @@
         <v>65</v>
       </c>
       <c r="O28" s="20">
-        <f>COUNTA(L28:N28)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3844,7 +4189,7 @@
         <v>65</v>
       </c>
       <c r="O29" s="20">
-        <f>COUNTA(L29:N29)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3892,7 +4237,7 @@
         <v>65</v>
       </c>
       <c r="O30" s="20">
-        <f>COUNTA(L30:N30)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -4015,7 +4360,7 @@
       </c>
       <c r="N2" s="10"/>
       <c r="O2" s="19">
-        <f>COUNTA(L2:N2)</f>
+        <f t="shared" ref="O2:O7" si="0">COUNTA(L2:N2)</f>
         <v>2</v>
       </c>
     </row>
@@ -4061,7 +4406,7 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="19">
-        <f>COUNTA(L3:N3)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -4107,7 +4452,7 @@
       </c>
       <c r="N4" s="13"/>
       <c r="O4" s="19">
-        <f>COUNTA(L4:N4)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -4153,7 +4498,7 @@
         <v>65</v>
       </c>
       <c r="O5" s="19">
-        <f>COUNTA(L5:N5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -4197,7 +4542,7 @@
         <v>65</v>
       </c>
       <c r="O6" s="19">
-        <f>COUNTA(L6:N6)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -4241,7 +4586,7 @@
         <v>65</v>
       </c>
       <c r="O7" s="19">
-        <f>COUNTA(L7:N7)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -4249,4 +4594,1525 @@
   <autoFilter ref="A1:K7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1A541B-90CE-4BCC-AFBC-461AF67DC2D9}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="35">
+        <v>34</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="67">
+        <v>1.57</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="35">
+        <v>1.36</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="45">
+        <v>1.18</v>
+      </c>
+      <c r="K2" s="32">
+        <v>1.18</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="72">
+        <v>51</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="74">
+        <v>1.29</v>
+      </c>
+      <c r="G3" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="78">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="67">
+        <v>2</v>
+      </c>
+      <c r="K3" s="32">
+        <v>1.29</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="35">
+        <v>67</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="64">
+        <v>5</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="81">
+        <v>2.1</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="74">
+        <v>1.25</v>
+      </c>
+      <c r="K4" s="76">
+        <v>1.25</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="35">
+        <v>67</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1.55</v>
+      </c>
+      <c r="G5" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="78">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="64">
+        <v>5.5</v>
+      </c>
+      <c r="K5" s="32">
+        <v>1.4</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="30">
+        <v>201</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="30">
+        <v>3.4</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="30">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="29">
+        <v>1.85</v>
+      </c>
+      <c r="K6" s="30">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="35">
+        <v>81</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G7" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="78">
+        <v>1.4</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="32">
+        <v>1.91</v>
+      </c>
+      <c r="K7" s="32">
+        <v>1.4</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="35">
+        <v>67</v>
+      </c>
+      <c r="E8" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="78">
+        <v>1.44</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32">
+        <v>1.44</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="27">
+        <v>5.5</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="27">
+        <v>21</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="27">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K9" s="27">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="27">
+        <v>751</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="27">
+        <v>9</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="27">
+        <v>7.5</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="K10" s="27">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="30">
+        <v>151</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="30">
+        <v>3.6</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="30">
+        <v>2.1</v>
+      </c>
+      <c r="K11" s="30">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="30">
+        <v>301</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="30">
+        <v>4.8</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="30">
+        <v>1.7</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="30">
+        <v>2.15</v>
+      </c>
+      <c r="K12" s="30">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="35">
+        <v>51</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="32">
+        <v>1.85</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="32">
+        <v>2.25</v>
+      </c>
+      <c r="K13" s="32">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="30">
+        <v>301</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="30">
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="30">
+        <v>4.5</v>
+      </c>
+      <c r="I14" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="54">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K14" s="30">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="38">
+        <v>81</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="46">
+        <v>5.5</v>
+      </c>
+      <c r="I15" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="51">
+        <v>1.25</v>
+      </c>
+      <c r="K15" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="35">
+        <v>51</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="32">
+        <v>1.91</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="I16" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="K16" s="32">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="38">
+        <v>81</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="30">
+        <v>1.83</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="30">
+        <v>2.88</v>
+      </c>
+      <c r="K17" s="30">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="30">
+        <v>301</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="30">
+        <v>8.5</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="30">
+        <v>1.7</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="30">
+        <v>3</v>
+      </c>
+      <c r="K18" s="30">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="27">
+        <v>501</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="27">
+        <v>6.5</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="27">
+        <v>3.1</v>
+      </c>
+      <c r="K19" s="27">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="38">
+        <v>67</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="30">
+        <v>1.83</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="30">
+        <v>5</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="30">
+        <v>3.2</v>
+      </c>
+      <c r="K20" s="30">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="35">
+        <v>34</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="35">
+        <v>1.33</v>
+      </c>
+      <c r="G21" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="78">
+        <v>1.44</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="32">
+        <v>3.3</v>
+      </c>
+      <c r="K21" s="32">
+        <v>1.33</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="27">
+        <v>501</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="27">
+        <v>8</v>
+      </c>
+      <c r="I22" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="27">
+        <v>3.3</v>
+      </c>
+      <c r="K22" s="27">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="43">
+        <v>101</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="32">
+        <v>7</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="I23" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="78">
+        <v>1.5</v>
+      </c>
+      <c r="K23" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="30">
+        <v>501</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="30">
+        <v>3.75</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="30">
+        <v>4.75</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" s="30">
+        <v>3.5</v>
+      </c>
+      <c r="K24" s="30">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="27">
+        <v>1501</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="27">
+        <v>6.5</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="27">
+        <v>13</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="27">
+        <v>3.5</v>
+      </c>
+      <c r="K25" s="27">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="27">
+        <v>36</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="27">
+        <v>7.5</v>
+      </c>
+      <c r="I26" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" s="63">
+        <v>3.75</v>
+      </c>
+      <c r="K26" s="27">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="30">
+        <v>251</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="30">
+        <v>1.95</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="46">
+        <v>9</v>
+      </c>
+      <c r="I27" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="69">
+        <v>4</v>
+      </c>
+      <c r="K27" s="47">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="35">
+        <v>29</v>
+      </c>
+      <c r="E28" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="71">
+        <v>1.29</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="32">
+        <v>2</v>
+      </c>
+      <c r="I28" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" s="64">
+        <v>5</v>
+      </c>
+      <c r="K28" s="32">
+        <v>1.29</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="52">
+        <v>101</v>
+      </c>
+      <c r="E29" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="85">
+        <v>1.35</v>
+      </c>
+      <c r="G29" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="54">
+        <v>5</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="30">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K29" s="30">
+        <v>1.35</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="43">
+        <v>101</v>
+      </c>
+      <c r="E30" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="83">
+        <v>2.38</v>
+      </c>
+      <c r="G30" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="74">
+        <v>1.22</v>
+      </c>
+      <c r="I30" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="J30" s="32">
+        <v>5.5</v>
+      </c>
+      <c r="K30" s="32">
+        <v>1.22</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="30">
+        <v>501</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="54">
+        <v>3.75</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="55">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="30">
+        <v>6.5</v>
+      </c>
+      <c r="K31" s="30">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="57">
+        <v>1001</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="61">
+        <v>8</v>
+      </c>
+      <c r="G32" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="27">
+        <v>20</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" s="27">
+        <v>6.5</v>
+      </c>
+      <c r="K32" s="27">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="30">
+        <v>151</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="55">
+        <v>1.8</v>
+      </c>
+      <c r="G33" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="78">
+        <v>1.5</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="30">
+        <v>3.5</v>
+      </c>
+      <c r="K33" s="30">
+        <v>1.5</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="27">
+        <v>2001</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="27">
+        <v>7</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="27">
+        <v>76</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="27">
+        <v>11</v>
+      </c>
+      <c r="K34" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="27">
+        <v>2001</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="27">
+        <v>67</v>
+      </c>
+      <c r="G35" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H35" s="63">
+        <v>13</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="27">
+        <v>12</v>
+      </c>
+      <c r="K35" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="57">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G36" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="61">
+        <v>5</v>
+      </c>
+      <c r="I36" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="27">
+        <v>15</v>
+      </c>
+      <c r="K36" s="27">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="27">
+        <v>2001</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="27">
+        <v>7.5</v>
+      </c>
+      <c r="G37" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="62">
+        <v>4.75</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" s="27">
+        <v>21</v>
+      </c>
+      <c r="K37" s="27">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="27">
+        <v>3.6</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="27">
+        <v>21</v>
+      </c>
+      <c r="K38" s="27">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="30">
+        <v>151</v>
+      </c>
+      <c r="E39" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="80">
+        <v>1.36</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="30">
+        <v>3.6</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="30">
+        <v>9</v>
+      </c>
+      <c r="K39" s="30">
+        <v>1.36</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="57">
+        <v>1001</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="61">
+        <v>9</v>
+      </c>
+      <c r="G40" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="27">
+        <v>7</v>
+      </c>
+      <c r="I40" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="26"/>
+      <c r="K40" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="30">
+        <v>201</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="55">
+        <v>2.62</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="29"/>
+      <c r="K41" s="30">
+        <v>2.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M41" xr:uid="{7C1A541B-90CE-4BCC-AFBC-461AF67DC2D9}">
+    <filterColumn colId="11">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="12">
+      <filters blank="1"/>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M39">
+      <sortCondition ref="D3:D41"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P2:Q18">
+    <sortCondition ref="Q3:Q18"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/lms_team_odds1.xlsx
+++ b/lms_team_odds1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paul_\Dropbox\Docs\lms2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB85ECC-BE0C-4484-9A35-DC75F23C307C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7047DCCF-D8C6-486A-A460-148907CB0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,7 +315,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +392,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAFF1B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -687,15 +693,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -774,28 +771,43 @@
     <xf numFmtId="2" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4598,7 +4610,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1A541B-90CE-4BCC-AFBC-461AF67DC2D9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4615,7 +4626,7 @@
     <col min="12" max="13" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4649,16 +4660,16 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B2" s="34" t="s">
         <v>18</v>
@@ -4667,39 +4678,36 @@
         <v>13</v>
       </c>
       <c r="D2" s="35">
-        <v>34</v>
-      </c>
-      <c r="E2" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="67">
-        <v>1.57</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="35">
-        <v>1.36</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="45">
-        <v>1.18</v>
+        <v>51</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="68">
+        <v>1.29</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="75">
+        <v>1.5</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="32">
+        <v>2</v>
       </c>
       <c r="K2" s="32">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M2" s="19" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>18</v>
@@ -4707,26 +4715,26 @@
       <c r="C3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="72">
-        <v>51</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="74">
+      <c r="D3" s="69">
+        <v>29</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="71">
         <v>1.29</v>
       </c>
-      <c r="G3" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="78">
-        <v>1.5</v>
-      </c>
-      <c r="I3" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="67">
+      <c r="G3" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="32">
         <v>2</v>
+      </c>
+      <c r="I3" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="64">
+        <v>5</v>
       </c>
       <c r="K3" s="32">
         <v>1.29</v>
@@ -4734,10 +4742,13 @@
       <c r="L3" s="19" t="s">
         <v>65</v>
       </c>
+      <c r="M3" s="19" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>18</v>
@@ -4746,109 +4757,115 @@
         <v>13</v>
       </c>
       <c r="D4" s="35">
-        <v>67</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="64">
+        <v>34</v>
+      </c>
+      <c r="E4" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="84">
+        <v>1.33</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="85">
+        <v>1.44</v>
+      </c>
+      <c r="I4" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="78">
+        <v>3.3</v>
+      </c>
+      <c r="K4" s="73">
+        <v>1.33</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="76">
+        <v>101</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="38">
+        <v>1.35</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="30">
         <v>5</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="I5" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="52">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K5" s="30">
+        <v>1.35</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" s="81">
-        <v>2.1</v>
-      </c>
-      <c r="I4" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="74">
-        <v>1.25</v>
-      </c>
-      <c r="K4" s="76">
-        <v>1.25</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="35">
-        <v>67</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="32">
-        <v>1.55</v>
-      </c>
-      <c r="G5" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="78">
-        <v>1.4</v>
-      </c>
-      <c r="I5" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="64">
-        <v>5.5</v>
-      </c>
-      <c r="K5" s="32">
-        <v>1.4</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>28</v>
+      <c r="C6" s="26" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="30">
-        <v>201</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="30">
-        <v>3.4</v>
+        <v>151</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="38">
+        <v>1.36</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H6" s="30">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="29">
-        <v>1.85</v>
+        <v>22</v>
+      </c>
+      <c r="J6" s="30">
+        <v>9</v>
       </c>
       <c r="K6" s="30">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>1.36</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>18</v>
@@ -4857,39 +4874,36 @@
         <v>13</v>
       </c>
       <c r="D7" s="35">
-        <v>81</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="32">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G7" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="78">
-        <v>1.4</v>
+        <v>67</v>
+      </c>
+      <c r="E7" s="74" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="75">
+        <v>1.44</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="32">
+        <v>1.8</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="32">
-        <v>1.91</v>
+        <v>47</v>
+      </c>
+      <c r="J7" s="31">
+        <v>1.85</v>
       </c>
       <c r="K7" s="32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="L7" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>18</v>
@@ -4900,67 +4914,75 @@
       <c r="D8" s="35">
         <v>67</v>
       </c>
-      <c r="E8" s="77" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="78">
-        <v>1.44</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="32">
-        <v>1.8</v>
+      <c r="E8" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1.55</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="75">
+        <v>1.4</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="31"/>
+        <v>56</v>
+      </c>
+      <c r="J8" s="32">
+        <v>5.5</v>
+      </c>
       <c r="K8" s="32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="L8" s="19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="27">
-        <v>1001</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="27">
-        <v>5.5</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="27">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="35">
+        <v>34</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="32">
+        <v>1.57</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="35">
+        <v>1.36</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="27">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="K9" s="27">
-        <v>2.0499999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="45">
+        <v>1.18</v>
+      </c>
+      <c r="K9" s="32">
+        <v>1.18</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>64</v>
@@ -4969,380 +4991,388 @@
         <v>13</v>
       </c>
       <c r="D10" s="27">
-        <v>751</v>
+        <v>501</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F10" s="27">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H10" s="27">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="J10" s="27">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="K10" s="27">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="29" t="s">
-        <v>28</v>
+      <c r="C11" s="26" t="s">
+        <v>13</v>
       </c>
       <c r="D11" s="30">
         <v>151</v>
       </c>
       <c r="E11" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1.8</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="75">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="30">
+        <v>3.5</v>
+      </c>
+      <c r="K11" s="30">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="38">
+        <v>81</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="30">
+        <v>1.83</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="30">
-        <v>3.6</v>
-      </c>
-      <c r="G11" s="29" t="s">
+      <c r="J12" s="30">
+        <v>2.88</v>
+      </c>
+      <c r="K12" s="30">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="38">
+        <v>67</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="30">
+        <v>1.83</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="30">
+        <v>5</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="30">
+        <v>3.2</v>
+      </c>
+      <c r="K13" s="30">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="35">
+        <v>51</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="32">
+        <v>1.91</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="I14" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" s="30">
-        <v>2.1</v>
-      </c>
-      <c r="K11" s="30">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="J14" s="64">
+        <v>2.4</v>
+      </c>
+      <c r="K14" s="32">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C15" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D15" s="30">
+        <v>251</v>
+      </c>
+      <c r="E15" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="88">
+        <v>1.95</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="46">
+        <v>9</v>
+      </c>
+      <c r="I15" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="66">
+        <v>4</v>
+      </c>
+      <c r="K15" s="47">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="43">
+        <v>101</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="32">
+        <v>2.38</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="45">
+        <v>1.22</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="61">
+        <v>5.5</v>
+      </c>
+      <c r="K16" s="32">
+        <v>1.22</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="30">
         <v>301</v>
       </c>
-      <c r="E12" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="30">
-        <v>4.8</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="30">
-        <v>1.7</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="30">
-        <v>2.15</v>
-      </c>
-      <c r="K12" s="30">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="35">
-        <v>51</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="32">
-        <v>3.5</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="32">
-        <v>1.85</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="32">
-        <v>2.25</v>
-      </c>
-      <c r="K13" s="32">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="30">
-        <v>301</v>
-      </c>
-      <c r="E14" s="29" t="s">
+      <c r="E17" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F17" s="30">
         <v>2.5</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G17" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H17" s="30">
         <v>4.5</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I17" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="54">
+      <c r="J17" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K17" s="30">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="38">
-        <v>81</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="30">
-        <v>2.9</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="46">
-        <v>5.5</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="51">
-        <v>1.25</v>
-      </c>
-      <c r="K15" s="47">
-        <v>1.25</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="35">
-        <v>51</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="32">
-        <v>1.91</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="I16" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="64">
-        <v>2.4</v>
-      </c>
-      <c r="K16" s="32">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="38">
-        <v>81</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="30">
-        <v>1.83</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="30">
-        <v>2.88</v>
-      </c>
-      <c r="K17" s="30">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="30">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F18" s="30">
-        <v>8.5</v>
+        <v>2.62</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="30">
-        <v>1.7</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H18" s="29"/>
       <c r="I18" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="30">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="J18" s="29">
+        <v>4.2</v>
       </c>
       <c r="K18" s="30">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>64</v>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>27</v>
       </c>
       <c r="C19" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="27">
-        <v>501</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="27">
+      <c r="D19" s="38">
+        <v>81</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="30">
+        <v>5.5</v>
+      </c>
+      <c r="I19" s="80" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="81">
+        <v>1.25</v>
+      </c>
+      <c r="K19" s="30">
+        <v>1.25</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="30">
+        <v>201</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="30">
+        <v>3.4</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="30">
         <v>6.5</v>
       </c>
-      <c r="G19" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="27">
-        <v>3.1</v>
-      </c>
-      <c r="K19" s="27">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="38">
-        <v>67</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="30">
-        <v>1.83</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="30">
-        <v>5</v>
-      </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="87">
+        <v>1.55</v>
+      </c>
+      <c r="K20" s="30">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
         <v>49</v>
-      </c>
-      <c r="J20" s="30">
-        <v>3.2</v>
-      </c>
-      <c r="K20" s="30">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>55</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>18</v>
@@ -5351,117 +5381,106 @@
         <v>13</v>
       </c>
       <c r="D21" s="35">
+        <v>51</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="32">
+        <v>1.85</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="32">
+        <v>2.25</v>
+      </c>
+      <c r="K21" s="32">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="30">
+        <v>151</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="30">
+        <v>3.6</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="30">
+        <v>2.1</v>
+      </c>
+      <c r="K22" s="30">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="35">
-        <v>1.33</v>
-      </c>
-      <c r="G21" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="78">
-        <v>1.44</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="32">
-        <v>3.3</v>
-      </c>
-      <c r="K21" s="32">
-        <v>1.33</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="27">
-        <v>501</v>
-      </c>
-      <c r="E22" s="26" t="s">
+      <c r="F23" s="27">
+        <v>3.6</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="27">
         <v>21</v>
       </c>
-      <c r="F22" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="27">
-        <v>8</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="27">
-        <v>3.3</v>
-      </c>
-      <c r="K22" s="27">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="43">
-        <v>101</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="32">
-        <v>7</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="H23" s="32">
-        <v>3.5</v>
-      </c>
-      <c r="I23" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="78">
-        <v>1.5</v>
-      </c>
-      <c r="K23" s="32">
-        <v>1.5</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="27">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>62</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="30">
@@ -5489,345 +5508,340 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="30">
+        <v>501</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="30">
+        <v>3.75</v>
+      </c>
+      <c r="G25" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="88">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="30">
+        <v>6.5</v>
+      </c>
+      <c r="K25" s="30">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="35">
+        <v>81</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G26" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="75">
+        <v>1.4</v>
+      </c>
+      <c r="I26" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="64">
+        <v>1.91</v>
+      </c>
+      <c r="K26" s="32">
+        <v>1.4</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="54">
+        <v>5</v>
+      </c>
+      <c r="I27" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="58">
+        <v>15</v>
+      </c>
+      <c r="K27" s="82">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="30">
+        <v>301</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="51">
+        <v>4.8</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="30">
+        <v>1.7</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="52">
+        <v>2.15</v>
+      </c>
+      <c r="K28" s="30">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="69">
+        <v>67</v>
+      </c>
+      <c r="E29" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="78">
+        <v>5</v>
+      </c>
+      <c r="G29" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="64">
+        <v>2.1</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="45">
+        <v>1.25</v>
+      </c>
+      <c r="K29" s="32">
+        <v>1.25</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="27">
+        <v>1001</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="79">
+        <v>5.5</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="58">
+        <v>21</v>
+      </c>
+      <c r="I30" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="27">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K30" s="27">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="27">
+        <v>501</v>
+      </c>
+      <c r="E31" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="60">
+        <v>6.5</v>
+      </c>
+      <c r="G31" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="56"/>
+      <c r="I31" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="27">
+        <v>3.1</v>
+      </c>
+      <c r="K31" s="27">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
         <v>54</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="27">
-        <v>1501</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="27">
-        <v>6.5</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="27">
-        <v>13</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="27">
-        <v>3.5</v>
-      </c>
-      <c r="K25" s="27">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="27">
-        <v>1001</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="27">
-        <v>36</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="H26" s="27">
-        <v>7.5</v>
-      </c>
-      <c r="I26" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="J26" s="63">
-        <v>3.75</v>
-      </c>
-      <c r="K26" s="27">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="30">
-        <v>251</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="30">
-        <v>1.95</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" s="46">
-        <v>9</v>
-      </c>
-      <c r="I27" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="69">
-        <v>4</v>
-      </c>
-      <c r="K27" s="47">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="35">
-        <v>29</v>
-      </c>
-      <c r="E28" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="71">
-        <v>1.29</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="H28" s="32">
-        <v>2</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" s="64">
-        <v>5</v>
-      </c>
-      <c r="K28" s="32">
-        <v>1.29</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M28" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="52">
-        <v>101</v>
-      </c>
-      <c r="E29" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="85">
-        <v>1.35</v>
-      </c>
-      <c r="G29" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="54">
-        <v>5</v>
-      </c>
-      <c r="I29" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="30">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K29" s="30">
-        <v>1.35</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="43">
-        <v>101</v>
-      </c>
-      <c r="E30" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="83">
-        <v>2.38</v>
-      </c>
-      <c r="G30" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="74">
-        <v>1.22</v>
-      </c>
-      <c r="I30" s="75" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="32">
-        <v>5.5</v>
-      </c>
-      <c r="K30" s="32">
-        <v>1.22</v>
-      </c>
-      <c r="L30" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="30">
-        <v>501</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="F31" s="54">
-        <v>3.75</v>
-      </c>
-      <c r="G31" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="H31" s="55">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="30">
-        <v>6.5</v>
-      </c>
-      <c r="K31" s="30">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
-        <v>38</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="57">
-        <v>1001</v>
-      </c>
-      <c r="E32" s="58" t="s">
+      <c r="C32" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="54">
+        <v>1501</v>
+      </c>
+      <c r="E32" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="58">
+        <v>6.5</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="27">
+        <v>13</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J32" s="27">
+        <v>3.5</v>
+      </c>
+      <c r="K32" s="27">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="43">
+        <v>101</v>
+      </c>
+      <c r="E33" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="61">
+        <v>7</v>
+      </c>
+      <c r="G33" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="61">
-        <v>8</v>
-      </c>
-      <c r="G32" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="H32" s="27">
-        <v>20</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="J32" s="27">
-        <v>6.5</v>
-      </c>
-      <c r="K32" s="27">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="30">
-        <v>151</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="55">
-        <v>1.8</v>
-      </c>
-      <c r="G33" s="77" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="78">
+      <c r="H33" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="I33" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="J33" s="75">
         <v>1.5</v>
       </c>
-      <c r="I33" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="30">
-        <v>3.5</v>
-      </c>
-      <c r="K33" s="30">
+      <c r="K33" s="32">
         <v>1.5</v>
       </c>
       <c r="L33" s="19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>24</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="26" t="s">
-        <v>13</v>
+      <c r="C34" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="D34" s="27">
         <v>2001</v>
@@ -5854,260 +5868,253 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>13</v>
+      <c r="C35" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="D35" s="27">
         <v>2001</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F35" s="27">
-        <v>67</v>
+        <v>7.5</v>
       </c>
       <c r="G35" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" s="63">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H35" s="60">
+        <v>4.75</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="J35" s="27">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K35" s="27">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="26" t="s">
-        <v>13</v>
+      <c r="C36" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="D36" s="27">
         <v>1001</v>
       </c>
       <c r="E36" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="54">
+        <v>8</v>
+      </c>
+      <c r="G36" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="58">
         <v>20</v>
       </c>
-      <c r="F36" s="57">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G36" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="61">
-        <v>5</v>
-      </c>
-      <c r="I36" s="65" t="s">
-        <v>17</v>
+      <c r="I36" s="62" t="s">
+        <v>37</v>
       </c>
       <c r="J36" s="27">
+        <v>6.5</v>
+      </c>
+      <c r="K36" s="27">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="30">
+        <v>301</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="30">
+        <v>8.5</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="52">
+        <v>1.7</v>
+      </c>
+      <c r="I37" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="K36" s="27">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="27">
-        <v>2001</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="27">
-        <v>7.5</v>
-      </c>
-      <c r="G37" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="62">
-        <v>4.75</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="J37" s="27">
-        <v>21</v>
-      </c>
-      <c r="K37" s="27">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J37" s="30">
+        <v>3</v>
+      </c>
+      <c r="K37" s="30">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="26" t="s">
-        <v>13</v>
+      <c r="C38" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="D38" s="27">
+        <v>751</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="27">
+        <v>9</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" s="27">
+        <v>7.5</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J38" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="K38" s="27">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="27">
         <v>1001</v>
       </c>
-      <c r="E38" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="27">
-        <v>3.6</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="H38" s="27">
-        <v>8.5</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="27">
-        <v>21</v>
-      </c>
-      <c r="K38" s="27">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="30">
-        <v>151</v>
-      </c>
-      <c r="E39" s="79" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="80">
-        <v>1.36</v>
-      </c>
-      <c r="G39" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="30">
-        <v>3.6</v>
-      </c>
-      <c r="I39" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" s="30">
+      <c r="E39" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="60">
         <v>9</v>
       </c>
-      <c r="K39" s="30">
-        <v>1.36</v>
-      </c>
-      <c r="L39" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G39" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="27">
+        <v>7</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="57">
+      <c r="C40" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="54">
         <v>1001</v>
       </c>
-      <c r="E40" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="61">
-        <v>9</v>
-      </c>
-      <c r="G40" s="65" t="s">
-        <v>26</v>
+      <c r="E40" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="58">
+        <v>36</v>
+      </c>
+      <c r="G40" s="62" t="s">
+        <v>59</v>
       </c>
       <c r="H40" s="27">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="26"/>
+        <v>58</v>
+      </c>
+      <c r="J40" s="27">
+        <v>3.75</v>
+      </c>
       <c r="K40" s="27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="29" t="s">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="30">
-        <v>201</v>
-      </c>
-      <c r="E41" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="55">
-        <v>2.62</v>
-      </c>
-      <c r="G41" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="J41" s="29"/>
-      <c r="K41" s="30">
-        <v>2.62</v>
+      <c r="D41" s="27">
+        <v>2001</v>
+      </c>
+      <c r="E41" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="59">
+        <v>67</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" s="27">
+        <v>13</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J41" s="27">
+        <v>12</v>
+      </c>
+      <c r="K41" s="27">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M41" xr:uid="{7C1A541B-90CE-4BCC-AFBC-461AF67DC2D9}">
-    <filterColumn colId="11">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="12">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M39">
-      <sortCondition ref="D3:D41"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
+      <sortCondition ref="F2:F41"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P2:Q18">
